--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,10 +96,10 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>90aba3dddaa9562f08223c81478bf6d85c260c39</t>
-  </si>
-  <si>
-    <t>Update Report.yml</t>
+    <t>2bc1061722fbb04ff9c358eca27a8580aaabbfa3</t>
+  </si>
+  <si>
+    <t>Update GeneralTest.md</t>
   </si>
 </sst>
 </file>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,7 +96,7 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>2bc1061722fbb04ff9c358eca27a8580aaabbfa3</t>
+    <t>4bce22539cfbd4831dea044e61fe953a5fc5fbed</t>
   </si>
   <si>
     <t>Update GeneralTest.md</t>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,7 +96,7 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>4bce22539cfbd4831dea044e61fe953a5fc5fbed</t>
+    <t>07d06016f20cbdc504329bcd126e5f620ba7293b</t>
   </si>
   <si>
     <t>Update GeneralTest.md</t>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,10 +96,10 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>07d06016f20cbdc504329bcd126e5f620ba7293b</t>
-  </si>
-  <si>
-    <t>Update GeneralTest.md</t>
+    <t>0211328ddd9f6cf7f11d28da4c51c290c7bd0e0d</t>
+  </si>
+  <si>
+    <t>add</t>
   </si>
 </sst>
 </file>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,7 +96,7 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>0211328ddd9f6cf7f11d28da4c51c290c7bd0e0d</t>
+    <t>ea12facec6e24aed98dd3ac1de55f88438af4b45</t>
   </si>
   <si>
     <t>add</t>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,10 +96,10 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>ea12facec6e24aed98dd3ac1de55f88438af4b45</t>
-  </si>
-  <si>
-    <t>add</t>
+    <t>415ae359e7faa9063a588810520ec06c551d6cc5</t>
+  </si>
+  <si>
+    <t>Update 001.md</t>
   </si>
 </sst>
 </file>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,10 +96,10 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>415ae359e7faa9063a588810520ec06c551d6cc5</t>
-  </si>
-  <si>
-    <t>Update 001.md</t>
+    <t>a10ab926c47df4082544d481e540d287efeba7b5</t>
+  </si>
+  <si>
+    <t>Update config.properties</t>
   </si>
 </sst>
 </file>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,10 +96,10 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>a10ab926c47df4082544d481e540d287efeba7b5</t>
-  </si>
-  <si>
-    <t>Update config.properties</t>
+    <t>0f629b6bbae022edba045c7acee5e571f6d8b8ea</t>
+  </si>
+  <si>
+    <t>Update 001.md</t>
   </si>
 </sst>
 </file>

--- a/Reports/GeneralTest.xlsx
+++ b/Reports/GeneralTest.xlsx
@@ -96,10 +96,10 @@
     <t>05/08/26 06:51:00</t>
   </si>
   <si>
-    <t>0f629b6bbae022edba045c7acee5e571f6d8b8ea</t>
-  </si>
-  <si>
-    <t>Update 001.md</t>
+    <t>05feda9710ef0d54a0daa57c178ae153669b7d82</t>
+  </si>
+  <si>
+    <t>Update GeneralTest.md</t>
   </si>
 </sst>
 </file>
